--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/35.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/35.xlsx
@@ -426,13 +426,13 @@
         <v>-6.120382387058127</v>
       </c>
       <c r="E2">
-        <v>-11.19343431565311</v>
+        <v>-8.115235808257236</v>
       </c>
       <c r="F2">
-        <v>-2.74026850856737</v>
+        <v>-1.977839151030705</v>
       </c>
       <c r="G2">
-        <v>-7.929622037037058</v>
+        <v>-6.414337514777691</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.503371378147279</v>
       </c>
       <c r="E3">
-        <v>-12.78694997726421</v>
+        <v>-8.818290454896074</v>
       </c>
       <c r="F3">
-        <v>-2.685544901203629</v>
+        <v>-2.060868072548105</v>
       </c>
       <c r="G3">
-        <v>-7.897682626377423</v>
+        <v>-6.206255568363945</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.953415533197288</v>
       </c>
       <c r="E4">
-        <v>-12.75928100107735</v>
+        <v>-9.663557299271792</v>
       </c>
       <c r="F4">
-        <v>-2.398194189581314</v>
+        <v>-1.463637541049537</v>
       </c>
       <c r="G4">
-        <v>-7.967733425450009</v>
+        <v>-6.085253960916303</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.376945004192198</v>
       </c>
       <c r="E5">
-        <v>-13.01089207389153</v>
+        <v>-10.48733653448111</v>
       </c>
       <c r="F5">
-        <v>-2.519496998577663</v>
+        <v>-1.39156046496455</v>
       </c>
       <c r="G5">
-        <v>-8.207141194091774</v>
+        <v>-5.594944304510038</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.738891909337509</v>
       </c>
       <c r="E6">
-        <v>-13.63909557365758</v>
+        <v>-10.56942418281815</v>
       </c>
       <c r="F6">
-        <v>-2.390430730282278</v>
+        <v>-1.480467481572215</v>
       </c>
       <c r="G6">
-        <v>-8.070232224523943</v>
+        <v>-5.705035850272528</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.981032130388609</v>
       </c>
       <c r="E7">
-        <v>-13.66824536084496</v>
+        <v>-11.25501703368342</v>
       </c>
       <c r="F7">
-        <v>-2.394717531591765</v>
+        <v>-1.210853772778643</v>
       </c>
       <c r="G7">
-        <v>-7.809519484296703</v>
+        <v>-5.89706606081747</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.053303987844755</v>
       </c>
       <c r="E8">
-        <v>-14.02528836550572</v>
+        <v>-12.51016058896739</v>
       </c>
       <c r="F8">
-        <v>-2.237933261631305</v>
+        <v>-1.116947558895083</v>
       </c>
       <c r="G8">
-        <v>-7.379249619985158</v>
+        <v>-5.574978071320817</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.917002723204034</v>
       </c>
       <c r="E9">
-        <v>-15.11165116604981</v>
+        <v>-11.32735034900793</v>
       </c>
       <c r="F9">
-        <v>-2.193217989228188</v>
+        <v>-1.2686299140217</v>
       </c>
       <c r="G9">
-        <v>-7.353990776420553</v>
+        <v>-5.403143779474257</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.554124736130811</v>
       </c>
       <c r="E10">
-        <v>-15.56410458957818</v>
+        <v>-12.69440608244346</v>
       </c>
       <c r="F10">
-        <v>-2.117560709228301</v>
+        <v>-1.416567220120261</v>
       </c>
       <c r="G10">
-        <v>-7.386783304685643</v>
+        <v>-5.171883283964593</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.970753208040282</v>
       </c>
       <c r="E11">
-        <v>-15.4857167045054</v>
+        <v>-14.42785159089158</v>
       </c>
       <c r="F11">
-        <v>-2.037953773451866</v>
+        <v>-1.005880885895128</v>
       </c>
       <c r="G11">
-        <v>-7.006581600149666</v>
+        <v>-4.487876556461188</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.20273537827853</v>
       </c>
       <c r="E12">
-        <v>-16.50955486442558</v>
+        <v>-12.88639979494666</v>
       </c>
       <c r="F12">
-        <v>-1.895923555302668</v>
+        <v>-1.325973647480496</v>
       </c>
       <c r="G12">
-        <v>-6.965300551710292</v>
+        <v>-4.646746741926383</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.29810689985265</v>
       </c>
       <c r="E13">
-        <v>-17.21386842683856</v>
+        <v>-13.83895524551211</v>
       </c>
       <c r="F13">
-        <v>-1.475119541619741</v>
+        <v>-1.397789787833602</v>
       </c>
       <c r="G13">
-        <v>-6.213546442669031</v>
+        <v>-3.472167860291957</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.325404914727009</v>
       </c>
       <c r="E14">
-        <v>-18.87331414152733</v>
+        <v>-15.59010708733022</v>
       </c>
       <c r="F14">
-        <v>-1.895111755247924</v>
+        <v>-0.7930741284833376</v>
       </c>
       <c r="G14">
-        <v>-6.28470301340715</v>
+        <v>-3.823672001069032</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.353003803464712</v>
       </c>
       <c r="E15">
-        <v>-19.40164667552823</v>
+        <v>-16.34190169971361</v>
       </c>
       <c r="F15">
-        <v>-1.57468267649702</v>
+        <v>-0.2531036653358827</v>
       </c>
       <c r="G15">
-        <v>-6.009139464401863</v>
+        <v>-3.58809013676558</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.441891515260829</v>
       </c>
       <c r="E16">
-        <v>-19.7636528877014</v>
+        <v>-17.00289587976921</v>
       </c>
       <c r="F16">
-        <v>-1.326357181587992</v>
+        <v>-0.3614980250944064</v>
       </c>
       <c r="G16">
-        <v>-5.270011495921347</v>
+        <v>-3.102443096195286</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.643324471545442</v>
       </c>
       <c r="E17">
-        <v>-21.00857567715006</v>
+        <v>-18.0481084370056</v>
       </c>
       <c r="F17">
-        <v>-0.9912775969511753</v>
+        <v>0.4026932699080131</v>
       </c>
       <c r="G17">
-        <v>-5.318442326138751</v>
+        <v>-1.558871162871946</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.9825657376993345</v>
       </c>
       <c r="E18">
-        <v>-20.94133236661016</v>
+        <v>-18.92378398434282</v>
       </c>
       <c r="F18">
-        <v>-0.4976310957030743</v>
+        <v>0.4125293044488544</v>
       </c>
       <c r="G18">
-        <v>-4.678476154406213</v>
+        <v>-1.880758997853473</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4689690934494998</v>
       </c>
       <c r="E19">
-        <v>-21.10292190462586</v>
+        <v>-18.49381443426254</v>
       </c>
       <c r="F19">
-        <v>-0.3833089388101174</v>
+        <v>0.3342676373345655</v>
       </c>
       <c r="G19">
-        <v>-4.793948903526191</v>
+        <v>-1.742035512763269</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.09100213114050226</v>
       </c>
       <c r="E20">
-        <v>-22.11182968574275</v>
+        <v>-17.18055244356412</v>
       </c>
       <c r="F20">
-        <v>0.04319672770627807</v>
+        <v>0.7887025392037491</v>
       </c>
       <c r="G20">
-        <v>-4.375790027990557</v>
+        <v>-1.445872454807789</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.1789537920882349</v>
       </c>
       <c r="E21">
-        <v>-22.17315428075462</v>
+        <v>-20.89815789542103</v>
       </c>
       <c r="F21">
-        <v>0.04836408356494138</v>
+        <v>0.6992512852124445</v>
       </c>
       <c r="G21">
-        <v>-3.728112985593324</v>
+        <v>-2.164125291727119</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.3682402938905726</v>
       </c>
       <c r="E22">
-        <v>-22.92412923934263</v>
+        <v>-20.84590836232053</v>
       </c>
       <c r="F22">
-        <v>0.03394303544960479</v>
+        <v>1.466664929411754</v>
       </c>
       <c r="G22">
-        <v>-3.874655621659684</v>
+        <v>-2.060074474855567</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.5099511103169561</v>
       </c>
       <c r="E23">
-        <v>-23.24791513089106</v>
+        <v>-22.44177430194162</v>
       </c>
       <c r="F23">
-        <v>0.1336204850284693</v>
+        <v>1.16556994584219</v>
       </c>
       <c r="G23">
-        <v>-4.355912387783441</v>
+        <v>-2.1094010785587</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6280024866273217</v>
       </c>
       <c r="E24">
-        <v>-24.61729849996653</v>
+        <v>-20.90874999612497</v>
       </c>
       <c r="F24">
-        <v>0.4094809124065523</v>
+        <v>2.001328042609473</v>
       </c>
       <c r="G24">
-        <v>-3.902260538639292</v>
+        <v>-1.689604873464902</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.7383343921180379</v>
       </c>
       <c r="E25">
-        <v>-24.47490969174335</v>
+        <v>-22.23370903518519</v>
       </c>
       <c r="F25">
-        <v>0.695481385162304</v>
+        <v>1.290910217559783</v>
       </c>
       <c r="G25">
-        <v>-4.271581712484152</v>
+        <v>-0.5341850445160752</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.8508225984689203</v>
       </c>
       <c r="E26">
-        <v>-23.93127091559654</v>
+        <v>-22.78813010794428</v>
       </c>
       <c r="F26">
-        <v>0.503377185881279</v>
+        <v>1.722984998125199</v>
       </c>
       <c r="G26">
-        <v>-3.616774575638245</v>
+        <v>-2.396393122255532</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.9651988668050518</v>
       </c>
       <c r="E27">
-        <v>-24.78287309510898</v>
+        <v>-21.98740986238201</v>
       </c>
       <c r="F27">
-        <v>0.5544079313633398</v>
+        <v>1.45777489044491</v>
       </c>
       <c r="G27">
-        <v>-3.960305348025869</v>
+        <v>-1.551941222938399</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.079292081863992</v>
       </c>
       <c r="E28">
-        <v>-24.49736186587338</v>
+        <v>-22.46286793386934</v>
       </c>
       <c r="F28">
-        <v>0.3886416736543251</v>
+        <v>1.689055069306532</v>
       </c>
       <c r="G28">
-        <v>-4.170871179160115</v>
+        <v>-2.185902759217154</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.185635128978415</v>
       </c>
       <c r="E29">
-        <v>-22.80239480106844</v>
+        <v>-19.97337104747062</v>
       </c>
       <c r="F29">
-        <v>0.2654891202475254</v>
+        <v>1.522919359735869</v>
       </c>
       <c r="G29">
-        <v>-4.202098564741351</v>
+        <v>-2.480366144404841</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.27530774395651</v>
       </c>
       <c r="E30">
-        <v>-23.69464456327373</v>
+        <v>-21.78538557995182</v>
       </c>
       <c r="F30">
-        <v>0.6245101795600535</v>
+        <v>1.983965461846795</v>
       </c>
       <c r="G30">
-        <v>-3.659899670594028</v>
+        <v>-0.9671553541710431</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.339313102894899</v>
       </c>
       <c r="E31">
-        <v>-22.78827049063851</v>
+        <v>-21.74968761934936</v>
       </c>
       <c r="F31">
-        <v>0.4206224539742056</v>
+        <v>1.437865908286027</v>
       </c>
       <c r="G31">
-        <v>-3.501564324243023</v>
+        <v>-1.070487583521076</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.370531162933838</v>
       </c>
       <c r="E32">
-        <v>-22.85177781012208</v>
+        <v>-20.67431995369589</v>
       </c>
       <c r="F32">
-        <v>0.3069149456941259</v>
+        <v>1.349740870506604</v>
       </c>
       <c r="G32">
-        <v>-3.656661104914856</v>
+        <v>-3.329595502312525</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.366621373841331</v>
       </c>
       <c r="E33">
-        <v>-22.47238225775946</v>
+        <v>-20.00980714933634</v>
       </c>
       <c r="F33">
-        <v>-0.1720089817040195</v>
+        <v>1.13608669324175</v>
       </c>
       <c r="G33">
-        <v>-3.418021142118001</v>
+        <v>-0.5341423886358024</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.328759297214853</v>
       </c>
       <c r="E34">
-        <v>-22.25045080359155</v>
+        <v>-19.15791514748739</v>
       </c>
       <c r="F34">
-        <v>-0.191933702843556</v>
+        <v>1.872950975993216</v>
       </c>
       <c r="G34">
-        <v>-3.602475012082186</v>
+        <v>-2.327018254824192</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.261839290814243</v>
       </c>
       <c r="E35">
-        <v>-21.51577382295715</v>
+        <v>-19.81097996955556</v>
       </c>
       <c r="F35">
-        <v>0.02423456948879459</v>
+        <v>1.671044705234865</v>
       </c>
       <c r="G35">
-        <v>-4.183051073588774</v>
+        <v>-2.542624042273745</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.171588479507453</v>
       </c>
       <c r="E36">
-        <v>-21.10637713029371</v>
+        <v>-17.49091593815382</v>
       </c>
       <c r="F36">
-        <v>0.3810074396701248</v>
+        <v>1.832100865891562</v>
       </c>
       <c r="G36">
-        <v>-3.833098950609317</v>
+        <v>-1.180736627918419</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.064120224009847</v>
       </c>
       <c r="E37">
-        <v>-21.03769376501938</v>
+        <v>-18.77299938530942</v>
       </c>
       <c r="F37">
-        <v>0.1869516067881043</v>
+        <v>1.873587162158566</v>
       </c>
       <c r="G37">
-        <v>-3.932159029488953</v>
+        <v>-2.684822340995401</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9450094922400936</v>
       </c>
       <c r="E38">
-        <v>-21.04443213434279</v>
+        <v>-19.07474972233653</v>
       </c>
       <c r="F38">
-        <v>0.09446935646995627</v>
+        <v>0.952815375576776</v>
       </c>
       <c r="G38">
-        <v>-3.855857503345625</v>
+        <v>-1.039998472790716</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.8174682294695026</v>
       </c>
       <c r="E39">
-        <v>-20.3477218797887</v>
+        <v>-18.33101579368679</v>
       </c>
       <c r="F39">
-        <v>0.2103123959144531</v>
+        <v>1.829698600423443</v>
       </c>
       <c r="G39">
-        <v>-3.945703912086341</v>
+        <v>-1.511532979433838</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6834479612425667</v>
       </c>
       <c r="E40">
-        <v>-19.38342862459537</v>
+        <v>-17.82042129237394</v>
       </c>
       <c r="F40">
-        <v>0.1427449519703058</v>
+        <v>1.594039671470623</v>
       </c>
       <c r="G40">
-        <v>-3.740138662608689</v>
+        <v>-1.226946071140079</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.5422807618662873</v>
       </c>
       <c r="E41">
-        <v>-18.74430244552282</v>
+        <v>-15.94355448362889</v>
       </c>
       <c r="F41">
-        <v>0.1311047332261672</v>
+        <v>1.45867449744435</v>
       </c>
       <c r="G41">
-        <v>-3.610139945645048</v>
+        <v>-1.02744451910428</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3944219362491354</v>
       </c>
       <c r="E42">
-        <v>-18.85691200867155</v>
+        <v>-16.36601129533045</v>
       </c>
       <c r="F42">
-        <v>-0.1218198575032031</v>
+        <v>0.8412922721378785</v>
       </c>
       <c r="G42">
-        <v>-4.169122288068931</v>
+        <v>-1.519306193308162</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.2442560194767751</v>
       </c>
       <c r="E43">
-        <v>-18.41222944654035</v>
+        <v>-15.70824591724232</v>
       </c>
       <c r="F43">
-        <v>0.3518248844369011</v>
+        <v>1.15463052592082</v>
       </c>
       <c r="G43">
-        <v>-4.261629767494356</v>
+        <v>-2.083981455137682</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.09878675517500057</v>
       </c>
       <c r="E44">
-        <v>-18.7061545804822</v>
+        <v>-15.88357031692329</v>
       </c>
       <c r="F44">
-        <v>-0.009565305647633644</v>
+        <v>0.7218963649027746</v>
       </c>
       <c r="G44">
-        <v>-4.066469271581703</v>
+        <v>-1.068223540645059</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.03237420209820772</v>
       </c>
       <c r="E45">
-        <v>-16.89753187503274</v>
+        <v>-15.18330068179917</v>
       </c>
       <c r="F45">
-        <v>0.1691756706914297</v>
+        <v>1.006352760819708</v>
       </c>
       <c r="G45">
-        <v>-4.428837536942099</v>
+        <v>-1.197677574829832</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1414249217949231</v>
       </c>
       <c r="E46">
-        <v>-16.9197032837743</v>
+        <v>-13.89676574469403</v>
       </c>
       <c r="F46">
-        <v>0.3748021394557537</v>
+        <v>0.9414568017495891</v>
       </c>
       <c r="G46">
-        <v>-4.714904276159168</v>
+        <v>-0.8012338235746023</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2220941946647838</v>
       </c>
       <c r="E47">
-        <v>-16.27899213879906</v>
+        <v>-14.76211637129376</v>
       </c>
       <c r="F47">
-        <v>0.1199507661474719</v>
+        <v>1.24615187005172</v>
       </c>
       <c r="G47">
-        <v>-3.963763755549524</v>
+        <v>-1.130553625388271</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.2675975823497788</v>
       </c>
       <c r="E48">
-        <v>-16.42827781293592</v>
+        <v>-13.27628329311105</v>
       </c>
       <c r="F48">
-        <v>-0.007414035502563327</v>
+        <v>1.090032779115709</v>
       </c>
       <c r="G48">
-        <v>-4.189193520348055</v>
+        <v>-1.381914884171093</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2732682957001953</v>
       </c>
       <c r="E49">
-        <v>-15.46957722314206</v>
+        <v>-13.84894958764704</v>
       </c>
       <c r="F49">
-        <v>-0.1714266394198515</v>
+        <v>0.4693735323637621</v>
       </c>
       <c r="G49">
-        <v>-4.252127349858204</v>
+        <v>-1.606852465735707</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.2365039992828404</v>
       </c>
       <c r="E50">
-        <v>-15.04668114946176</v>
+        <v>-12.90826326745569</v>
       </c>
       <c r="F50">
-        <v>-0.05548833772403264</v>
+        <v>0.6382329139548302</v>
       </c>
       <c r="G50">
-        <v>-4.569021165626256</v>
+        <v>-2.160899850934185</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.1559090614617143</v>
       </c>
       <c r="E51">
-        <v>-14.79250243188523</v>
+        <v>-11.68872710329404</v>
       </c>
       <c r="F51">
-        <v>-0.05360463025006656</v>
+        <v>0.4904985578699551</v>
       </c>
       <c r="G51">
-        <v>-4.385079166225345</v>
+        <v>-1.293810804078443</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.03505323278558158</v>
       </c>
       <c r="E52">
-        <v>-13.97984060036474</v>
+        <v>-11.10248444368306</v>
       </c>
       <c r="F52">
-        <v>0.0322556510501022</v>
+        <v>0.29997736869568</v>
       </c>
       <c r="G52">
-        <v>-4.987878941354052</v>
+        <v>-1.780924550685808</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.1209519135928678</v>
       </c>
       <c r="E53">
-        <v>-12.32566150094688</v>
+        <v>-11.98079103441874</v>
       </c>
       <c r="F53">
-        <v>-0.1503960477975776</v>
+        <v>1.056946128313091</v>
       </c>
       <c r="G53">
-        <v>-5.105235111649152</v>
+        <v>-1.54207130848759</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.3047552346009864</v>
       </c>
       <c r="E54">
-        <v>-12.93128150083668</v>
+        <v>-10.96525356735461</v>
       </c>
       <c r="F54">
-        <v>-0.2728983327931797</v>
+        <v>-0.1084317835391574</v>
       </c>
       <c r="G54">
-        <v>-4.293703708237929</v>
+        <v>-1.445590269753677</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.5056424556213143</v>
       </c>
       <c r="E55">
-        <v>-11.91542251211802</v>
+        <v>-10.92038544688661</v>
       </c>
       <c r="F55">
-        <v>0.05209670708195595</v>
+        <v>0.6643364275518482</v>
       </c>
       <c r="G55">
-        <v>-5.067871841751755</v>
+        <v>-1.940956288583046</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.7130093789036193</v>
       </c>
       <c r="E56">
-        <v>-12.16920725245588</v>
+        <v>-9.775310980833082</v>
       </c>
       <c r="F56">
-        <v>-0.2778743357817963</v>
+        <v>0.4586643985803701</v>
       </c>
       <c r="G56">
-        <v>-5.32802349309233</v>
+        <v>-3.524336001865569</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9143377559428327</v>
       </c>
       <c r="E57">
-        <v>-11.2361740533375</v>
+        <v>-9.500283168925238</v>
       </c>
       <c r="F57">
-        <v>-0.2293253790385229</v>
+        <v>0.5739698275804501</v>
       </c>
       <c r="G57">
-        <v>-5.541332425450271</v>
+        <v>-1.089768041404373</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.097186310309403</v>
       </c>
       <c r="E58">
-        <v>-12.2913718957608</v>
+        <v>-8.231549663144248</v>
       </c>
       <c r="F58">
-        <v>-0.2807330316888574</v>
+        <v>0.1903503982417906</v>
       </c>
       <c r="G58">
-        <v>-6.088633619122531</v>
+        <v>-2.704509670352069</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.251485062562126</v>
       </c>
       <c r="E59">
-        <v>-11.5845586156956</v>
+        <v>-8.721489794508113</v>
       </c>
       <c r="F59">
-        <v>-0.1015720730765747</v>
+        <v>0.5376136106389826</v>
       </c>
       <c r="G59">
-        <v>-5.464351686444139</v>
+        <v>-2.279811320248461</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.369294593566237</v>
       </c>
       <c r="E60">
-        <v>-10.73468178478007</v>
+        <v>-8.48936021687493</v>
       </c>
       <c r="F60">
-        <v>-0.6643996779694764</v>
+        <v>0.2281786240580329</v>
       </c>
       <c r="G60">
-        <v>-5.399662403399685</v>
+        <v>-2.059434636651476</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.44786896384056</v>
       </c>
       <c r="E61">
-        <v>-10.51707955176349</v>
+        <v>-8.178435191508283</v>
       </c>
       <c r="F61">
-        <v>-0.3438198363512622</v>
+        <v>-0.2792055221980951</v>
       </c>
       <c r="G61">
-        <v>-5.954749935832508</v>
+        <v>-2.067371911603773</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.48846783930367</v>
       </c>
       <c r="E62">
-        <v>-9.998537578567184</v>
+        <v>-8.128889157390361</v>
       </c>
       <c r="F62">
-        <v>-0.741356666424356</v>
+        <v>0.679615664296485</v>
       </c>
       <c r="G62">
-        <v>-5.438154413513532</v>
+        <v>-2.800816804343331</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.495635005819349</v>
       </c>
       <c r="E63">
-        <v>-9.664422237807257</v>
+        <v>-8.112423625898472</v>
       </c>
       <c r="F63">
-        <v>-0.4234093764122386</v>
+        <v>0.1439104649060448</v>
       </c>
       <c r="G63">
-        <v>-6.022628566232741</v>
+        <v>-2.302586279092567</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.477236987549068</v>
       </c>
       <c r="E64">
-        <v>-9.862787513239249</v>
+        <v>-8.734155936307566</v>
       </c>
       <c r="F64">
-        <v>-0.8401171132883215</v>
+        <v>-0.03348110093385817</v>
       </c>
       <c r="G64">
-        <v>-6.490415917854977</v>
+        <v>-2.397735141873345</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.441117009879315</v>
       </c>
       <c r="E65">
-        <v>-9.670350010283297</v>
+        <v>-7.713514879036798</v>
       </c>
       <c r="F65">
-        <v>-0.6981622765727786</v>
+        <v>-0.5080693533457509</v>
       </c>
       <c r="G65">
-        <v>-5.850955054242593</v>
+        <v>-4.02116872673201</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.395048053113364</v>
       </c>
       <c r="E66">
-        <v>-9.420364659637871</v>
+        <v>-6.217397636382665</v>
       </c>
       <c r="F66">
-        <v>-1.065126550910751</v>
+        <v>-0.3626552543561173</v>
       </c>
       <c r="G66">
-        <v>-6.096994171655996</v>
+        <v>-3.451998191366051</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.345640057517244</v>
       </c>
       <c r="E67">
-        <v>-8.722784938074305</v>
+        <v>-6.625856934926516</v>
       </c>
       <c r="F67">
-        <v>-0.9794874437071299</v>
+        <v>-0.1665425852129455</v>
       </c>
       <c r="G67">
-        <v>-5.494729235641477</v>
+        <v>-2.981372583094895</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.298423906780192</v>
       </c>
       <c r="E68">
-        <v>-9.51697512411751</v>
+        <v>-8.377846544436046</v>
       </c>
       <c r="F68">
-        <v>-1.001884841544023</v>
+        <v>-0.2640521972986838</v>
       </c>
       <c r="G68">
-        <v>-6.682521596495786</v>
+        <v>-3.84590555835583</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.260643190166121</v>
       </c>
       <c r="E69">
-        <v>-9.250456314870078</v>
+        <v>-7.129459472371521</v>
       </c>
       <c r="F69">
-        <v>-0.966745496317268</v>
+        <v>-0.4844989872664938</v>
       </c>
       <c r="G69">
-        <v>-6.411883161051227</v>
+        <v>-3.52746300601172</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.236583881747254</v>
       </c>
       <c r="E70">
-        <v>-9.493907077522437</v>
+        <v>-7.131954661549748</v>
       </c>
       <c r="F70">
-        <v>-1.180383106234066</v>
+        <v>-0.765085250677548</v>
       </c>
       <c r="G70">
-        <v>-5.802940939163238</v>
+        <v>-3.118606393597111</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.228445439715665</v>
       </c>
       <c r="E71">
-        <v>-9.28762150105103</v>
+        <v>-6.925623800338263</v>
       </c>
       <c r="F71">
-        <v>-1.413691128497741</v>
+        <v>-0.4891080234956702</v>
       </c>
       <c r="G71">
-        <v>-5.901758207647475</v>
+        <v>-3.6875964617773</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.233408378346639</v>
       </c>
       <c r="E72">
-        <v>-9.988090389031488</v>
+        <v>-7.632812943746105</v>
       </c>
       <c r="F72">
-        <v>-1.141871477310514</v>
+        <v>-1.359710566694311</v>
       </c>
       <c r="G72">
-        <v>-5.471704903958854</v>
+        <v>-4.020830760911386</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.245135343565367</v>
       </c>
       <c r="E73">
-        <v>-9.758288447038248</v>
+        <v>-7.08840885549199</v>
       </c>
       <c r="F73">
-        <v>-1.777829841624765</v>
+        <v>-0.8802018119097896</v>
       </c>
       <c r="G73">
-        <v>-5.235588200541212</v>
+        <v>-3.593648526087279</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.257254230068162</v>
       </c>
       <c r="E74">
-        <v>-10.46671386385018</v>
+        <v>-7.930849932086922</v>
       </c>
       <c r="F74">
-        <v>-1.856962951246799</v>
+        <v>-1.139738431248305</v>
       </c>
       <c r="G74">
-        <v>-5.151857988787302</v>
+        <v>-2.791668758635599</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.261720148629379</v>
       </c>
       <c r="E75">
-        <v>-10.56076121204148</v>
+        <v>-7.804962883147693</v>
       </c>
       <c r="F75">
-        <v>-1.822488785044492</v>
+        <v>-0.7770427341369588</v>
       </c>
       <c r="G75">
-        <v>-5.011792484079286</v>
+        <v>-2.508896365864213</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.253215926277339</v>
       </c>
       <c r="E76">
-        <v>-10.90518335964287</v>
+        <v>-8.407195584479759</v>
       </c>
       <c r="F76">
-        <v>-1.548396922071386</v>
+        <v>-1.118344186336203</v>
       </c>
       <c r="G76">
-        <v>-4.673554322067046</v>
+        <v>-2.035557187363397</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.228497084764103</v>
       </c>
       <c r="E77">
-        <v>-10.34381107928201</v>
+        <v>-8.630032733449202</v>
       </c>
       <c r="F77">
-        <v>-1.86478688136624</v>
+        <v>-1.523227806904725</v>
       </c>
       <c r="G77">
-        <v>-5.346486926807325</v>
+        <v>-2.672094482566315</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.185327008155812</v>
       </c>
       <c r="E78">
-        <v>-11.31148257608506</v>
+        <v>-9.080941947340955</v>
       </c>
       <c r="F78">
-        <v>-1.666146863277127</v>
+        <v>-1.177930310354377</v>
       </c>
       <c r="G78">
-        <v>-4.400635437638672</v>
+        <v>-2.553826132677689</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.123314848481994</v>
       </c>
       <c r="E79">
-        <v>-11.85848600841958</v>
+        <v>-11.76903053287205</v>
       </c>
       <c r="F79">
-        <v>-1.882452644598342</v>
+        <v>-1.124933849025473</v>
       </c>
       <c r="G79">
-        <v>-4.256386375442363</v>
+        <v>-4.131361990362842</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.041179414914699</v>
       </c>
       <c r="E80">
-        <v>-11.83619233087981</v>
+        <v>-9.452987786389128</v>
       </c>
       <c r="F80">
-        <v>-1.948162888825413</v>
+        <v>-1.367590825797143</v>
       </c>
       <c r="G80">
-        <v>-4.390243808959911</v>
+        <v>-1.953890863970377</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.939438704474967</v>
       </c>
       <c r="E81">
-        <v>-12.21720907693718</v>
+        <v>-9.946582396277181</v>
       </c>
       <c r="F81">
-        <v>-1.765247769143643</v>
+        <v>-2.011535480241784</v>
       </c>
       <c r="G81">
-        <v>-3.608420585547899</v>
+        <v>-2.361100303162145</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8169163668506291</v>
       </c>
       <c r="E82">
-        <v>-14.40999128940533</v>
+        <v>-12.03786792081141</v>
       </c>
       <c r="F82">
-        <v>-2.022338219541692</v>
+        <v>-1.905919464752249</v>
       </c>
       <c r="G82">
-        <v>-3.940490051028383</v>
+        <v>-2.725739173841677</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.6708814756457372</v>
       </c>
       <c r="E83">
-        <v>-13.83996962368983</v>
+        <v>-12.60612348166393</v>
       </c>
       <c r="F83">
-        <v>-2.286483875109385</v>
+        <v>-1.653715553663315</v>
       </c>
       <c r="G83">
-        <v>-3.293623470356333</v>
+        <v>-2.73789281849786</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.4992478262563555</v>
       </c>
       <c r="E84">
-        <v>-15.70425633164156</v>
+        <v>-13.90061947607455</v>
       </c>
       <c r="F84">
-        <v>-2.471920545165276</v>
+        <v>-1.38311857276262</v>
       </c>
       <c r="G84">
-        <v>-4.49655210626436</v>
+        <v>-1.744430804501664</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2985370385600585</v>
       </c>
       <c r="E85">
-        <v>-15.80210759799931</v>
+        <v>-14.79348058227089</v>
       </c>
       <c r="F85">
-        <v>-2.314741143953681</v>
+        <v>-1.752814802795025</v>
       </c>
       <c r="G85">
-        <v>-3.090341951084054</v>
+        <v>-1.83823108522151</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.0671457410124735</v>
       </c>
       <c r="E86">
-        <v>-17.34379940306663</v>
+        <v>-15.54369475722561</v>
       </c>
       <c r="F86">
-        <v>-2.661134570577933</v>
+        <v>-2.036171126801041</v>
       </c>
       <c r="G86">
-        <v>-3.062625472571425</v>
+        <v>-0.731868799807941</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.198198254086359</v>
       </c>
       <c r="E87">
-        <v>-18.58419824698163</v>
+        <v>-17.0859571500179</v>
       </c>
       <c r="F87">
-        <v>-2.72837315266317</v>
+        <v>-1.679092589048078</v>
       </c>
       <c r="G87">
-        <v>-3.220110982538533</v>
+        <v>-2.464435813733737</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4972774507413322</v>
       </c>
       <c r="E88">
-        <v>-19.75848589885864</v>
+        <v>-17.81591998921031</v>
       </c>
       <c r="F88">
-        <v>-2.693570952969354</v>
+        <v>-2.064153377667608</v>
       </c>
       <c r="G88">
-        <v>-2.990195787868242</v>
+        <v>-1.30505555036266</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8239686385585583</v>
       </c>
       <c r="E89">
-        <v>-21.61086272017021</v>
+        <v>-20.95465060866671</v>
       </c>
       <c r="F89">
-        <v>-2.939688020382518</v>
+        <v>-1.964235701541932</v>
       </c>
       <c r="G89">
-        <v>-2.791163450515445</v>
+        <v>-1.692315162473004</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.171590623343759</v>
       </c>
       <c r="E90">
-        <v>-22.44711337279666</v>
+        <v>-23.60867601271212</v>
       </c>
       <c r="F90">
-        <v>-3.112862367774768</v>
+        <v>-1.751843956198944</v>
       </c>
       <c r="G90">
-        <v>-3.091362410989042</v>
+        <v>-1.952361814723676</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.529089323811411</v>
       </c>
       <c r="E91">
-        <v>-24.57985254839711</v>
+        <v>-22.03134964567844</v>
       </c>
       <c r="F91">
-        <v>-3.04746358969115</v>
+        <v>-2.374370343076801</v>
       </c>
       <c r="G91">
-        <v>-2.551178186879218</v>
+        <v>-0.1905098983798356</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.884161087111972</v>
       </c>
       <c r="E92">
-        <v>-26.25496225467842</v>
+        <v>-25.34453066933232</v>
       </c>
       <c r="F92">
-        <v>-3.438662580765425</v>
+        <v>-2.29056606967038</v>
       </c>
       <c r="G92">
-        <v>-2.953885790091427</v>
+        <v>-1.461395914005522</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.2221351417128</v>
       </c>
       <c r="E93">
-        <v>-28.06520615382262</v>
+        <v>-26.39116969588112</v>
       </c>
       <c r="F93">
-        <v>-3.536965768823045</v>
+        <v>-2.893711144424937</v>
       </c>
       <c r="G93">
-        <v>-2.809344699176328</v>
+        <v>-1.887439564948503</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.526637907177241</v>
       </c>
       <c r="E94">
-        <v>-29.96187371516621</v>
+        <v>-28.60746827387111</v>
       </c>
       <c r="F94">
-        <v>-3.74574086208541</v>
+        <v>-2.773701416944359</v>
       </c>
       <c r="G94">
-        <v>-3.326117407459514</v>
+        <v>-0.8556594455811117</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.788439786253258</v>
       </c>
       <c r="E95">
-        <v>-32.13768773552761</v>
+        <v>-32.05544838331132</v>
       </c>
       <c r="F95">
-        <v>-3.355088593496983</v>
+        <v>-2.69855275452979</v>
       </c>
       <c r="G95">
-        <v>-2.80998125615886</v>
+        <v>-2.472501056326852</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.997609330642837</v>
       </c>
       <c r="E96">
-        <v>-34.10129972812659</v>
+        <v>-33.2265298755909</v>
       </c>
       <c r="F96">
-        <v>-3.535772091395611</v>
+        <v>-2.888494086522106</v>
       </c>
       <c r="G96">
-        <v>-2.926293997998056</v>
+        <v>-1.904718477680539</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.152978479548438</v>
       </c>
       <c r="E97">
-        <v>-36.74437981049546</v>
+        <v>-36.38956255080947</v>
       </c>
       <c r="F97">
-        <v>-3.700039832472962</v>
+        <v>-3.303094456725467</v>
       </c>
       <c r="G97">
-        <v>-3.367007990533314</v>
+        <v>-1.558618508811869</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.253998482411739</v>
       </c>
       <c r="E98">
-        <v>-39.1005199300793</v>
+        <v>-36.79353413161171</v>
       </c>
       <c r="F98">
-        <v>-4.03682419722474</v>
+        <v>-3.481108954852274</v>
       </c>
       <c r="G98">
-        <v>-3.958871454204392</v>
+        <v>-0.4347016880552708</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.305923647522994</v>
       </c>
       <c r="E99">
-        <v>-41.34043223578228</v>
+        <v>-42.40505836108955</v>
       </c>
       <c r="F99">
-        <v>-4.202063613265574</v>
+        <v>-3.411378643619418</v>
       </c>
       <c r="G99">
-        <v>-3.430056662798044</v>
+        <v>-2.144779209412633</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.307730055636834</v>
       </c>
       <c r="E100">
-        <v>-44.42027005076893</v>
+        <v>-42.96396488735323</v>
       </c>
       <c r="F100">
-        <v>-4.31479944658217</v>
+        <v>-2.913542260047957</v>
       </c>
       <c r="G100">
-        <v>-3.690739872031248</v>
+        <v>-1.761440657065825</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.270636553252787</v>
       </c>
       <c r="E101">
-        <v>-46.25799499442868</v>
+        <v>-44.59488121579368</v>
       </c>
       <c r="F101">
-        <v>-4.492693831435572</v>
+        <v>-3.898503408305278</v>
       </c>
       <c r="G101">
-        <v>-3.928890932815746</v>
+        <v>-2.437582296491241</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.175496259954968</v>
       </c>
       <c r="E102">
-        <v>-49.48166620084695</v>
+        <v>-47.69100115907491</v>
       </c>
       <c r="F102">
-        <v>-4.583602183688401</v>
+        <v>-3.585885834162773</v>
       </c>
       <c r="G102">
-        <v>-4.504285945479971</v>
+        <v>-1.817208298690148</v>
       </c>
     </row>
   </sheetData>
